--- a/data/google_news_dedup_audit_09_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_09_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,457 +451,58 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7053792476654053</v>
+        <v>0.7071912288665771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Levi Strauss shares rise as pricey denim sales smooth over tariff hit - Reuters</t>
+          <t>Amazon Pharmacy to Offer Eli Lilly and Company’s New GLP-1 Pill Foundayo via Same-Day Delivery - Business Wire</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Levi Strauss raises annual forecasts on resilient demand for premium jeans - MSN</t>
+          <t>Amazon to stock Lilly's new weight-loss pill at US kiosks, offer same-day delivery - Reuters</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7053792476654053</v>
+        <v>0.9872242212295532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Levi Strauss shares rise as pricey denim sales smooth over tariff hit - Reuters</t>
+          <t>Les perturbations restent importantes chez Bpost en Wallonie: celles en Flandre sont quasi terminées - 7sur7.be</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Levi Strauss raises annual forecasts on resilient demand for premium jeans - MSN</t>
+          <t>Les perturbations encore importantes chez Bpost en Wallonie: celles en Flandre quasi terminées - 7sur7.be</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7269655466079712</v>
+        <v>0.7035248875617981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon and U.S. Postal Service Reach New Deal on Deliveries After Year of Talks - The New York Times</t>
+          <t>‘I’m broken-hearted’: father pays tribute to student, 21, stabbed in Primrose Hill - The Guardian</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Amazon keeps 80% of USPS deliveries in new deal, over 1B packages yearly - 24/7 Wall St.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B5" t="n">
-        <v>31</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.744140088558197</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Certains conducteurs ont dix fois plus de chances d’être contrôlés pour alcool au volant selon la commune : voici où la police mène le plus d’actions en Belgique - RTL Info</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Alcool au volant : pourquoi certains conducteurs ont jusqu’à dix fois plus de risques d’être contrôlés - Le Soir</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>36</v>
-      </c>
-      <c r="B6" t="n">
-        <v>37</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9870625138282776</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Suffolk County police rescue teen stuck in mud at Wertheim National Wildlife Refuge - MSN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Suffolk County police rescue teen stuck in mud at Wertheim National Wildlife Refuge - AOL.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B7" t="n">
-        <v>46</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6357873678207397</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Man, 21, killed in Primrose Hill stabbing named by police - ITVX</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>Musician’s heartbreak as son, 21, stabbed to death on Primrose Hill - London Evening Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B8" t="n">
-        <v>47</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.771694540977478</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Man, 21, killed in Primrose Hill stabbing named by police - ITVX</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Primrose Hill stabbings: video director, 21, killed in north London park - The Times</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>44</v>
-      </c>
-      <c r="B9" t="n">
-        <v>53</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7911320924758911</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Man, 21, killed in Primrose Hill stabbing named by police - ITVX</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Primrose Hill stabbing: Man, 21, dies in fight at north London beauty spot as ‘crowds enjoy sunshine’ - Yahoo News Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>44</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.9132667183876038</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Man, 21, killed in Primrose Hill stabbing named by police - ITVX</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>44</v>
-      </c>
-      <c r="B11" t="n">
-        <v>62</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.8516244292259216</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Man, 21, killed in Primrose Hill stabbing named by police - ITVX</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Man, 21, stabbed to death in Primrose Hill named and pictured - My London</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>44</v>
-      </c>
-      <c r="B12" t="n">
-        <v>63</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8416417837142944</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Man, 21, killed in Primrose Hill stabbing named by police - ITVX</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Man, 21, stabbed to death in Primrose Hill named and pictured for first time - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>44</v>
-      </c>
-      <c r="B13" t="n">
-        <v>69</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.7419843673706055</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Man, 21, killed in Primrose Hill stabbing named by police - ITVX</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Man, 21, stabbed to death in Primrose Hill was 'music video director' - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>45</v>
-      </c>
-      <c r="B14" t="n">
-        <v>48</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.8652176260948181</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Primrose Hill stab victim named as Finbar Sullivan - BBC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Finbar Sullivan named as 21-year-old victim of Primrose Hill stabbing - Sky News</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>49</v>
-      </c>
-      <c r="B15" t="n">
-        <v>54</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.5928287506103516</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Two dead after separate double stabbings just hours apart in London - The Independent</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Police launch murder investigation as man dies after double stabbing in Shadwell - East London Advertiser</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>49</v>
-      </c>
-      <c r="B16" t="n">
-        <v>59</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.6990399360656738</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Two dead after separate double stabbings just hours apart in London - The Independent</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Two people taken to hospital after double stabbing in Shadwell - East London Advertiser</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>49</v>
-      </c>
-      <c r="B17" t="n">
-        <v>60</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.5044711232185364</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Two dead after separate double stabbings just hours apart in London - The Independent</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Murder investigation after man's death in Shadwell, east London - BBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>49</v>
-      </c>
-      <c r="B18" t="n">
-        <v>65</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.7217569351196289</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Two dead after separate double stabbings just hours apart in London - The Independent</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Forensics at London viewpoint after man killed and another injured in double stabbing - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>49</v>
-      </c>
-      <c r="B19" t="n">
-        <v>68</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.9416792392730713</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Two dead after separate double stabbings just hours apart in London - The Independent</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Two dead in two separate double stabbings less than three hours apart in London - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>55</v>
-      </c>
-      <c r="B20" t="n">
-        <v>58</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.7215947508811951</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bomb squad called after Tate Modern evacuated and Millennium Bridge closed - Metro.co.uk</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Tate Modern evacuated and Millennium Bridge closed in police incident - London Evening Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>70</v>
-      </c>
-      <c r="B21" t="n">
-        <v>80</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.7192429304122925</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Sanità lombarda, il diritto alla cura passa da chi cura: l’11 aprile in piazza a Milano - FP CGIL Lombardia</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Anche la Cgil di Sondrio scende in piazza per il rilancio della sanità pubblica lombarda - SondrioToday</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>73</v>
-      </c>
-      <c r="B22" t="n">
-        <v>83</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.7166112661361694</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Federconsumatori sul blocco dei treni per la frana in Molise: "Servono collegamenti regionali veloci Pescara - Bologna" - IlPescara</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>E' caos treni dopo la frana: da Bologna convogli deviati - BolognaToday</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>75</v>
-      </c>
-      <c r="B23" t="n">
-        <v>88</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.7924838066101074</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Sciopero aerei del 10 aprile: quattro ore di stop, Caselle a rischio disagi - Quotidiano Piemontese</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sciopero 10 aprile 2026: aerei a rischio per quattro ore - Icona Meteo</t>
         </is>
       </c>
     </row>
